--- a/AI Audit Log_NguyenVanTuanAnh.xlsx
+++ b/AI Audit Log_NguyenVanTuanAnh.xlsx
@@ -4,11 +4,12 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="6310" activeTab="1"/>
+    <workbookView windowWidth="19200" windowHeight="7510" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Week 1" sheetId="1" r:id="rId1"/>
     <sheet name="Week 2" sheetId="2" r:id="rId2"/>
+    <sheet name="Week 3" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -28,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="46">
   <si>
     <t>STT</t>
   </si>
@@ -52,6 +53,9 @@
 Quyết định: Tôi giữ lại 7 module làm nền, nhưng nhận ra AI chỉ mô tả những gì nhìn thấy từ màn hình Student. Tôi quyết định bổ sung thêm 4 module ẩn (Authentication, Premium, Moderator, Admin) dựa trên yêu cầu nghiệp vụ thực tế của hệ thống.</t>
   </si>
   <si>
+    <t xml:space="preserve"> </t>
+  </si>
+  <si>
     <t>Abstraction</t>
   </si>
   <si>
@@ -146,6 +150,102 @@
   </si>
   <si>
     <t/>
+  </si>
+  <si>
+    <t>Abstraction + Decomposition</t>
+  </si>
+  <si>
+    <t>"Dựa trên actor và feature của hệ thống SEHUB, hãy tạo toàn bộ Use Case và nhóm theo từng module chức năng."</t>
+  </si>
+  <si>
+    <r>
+      <t>Phản hồi:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> AI liệt kê các Use Case theo nhóm Authentication, Community, Exam, Document, Premium, Moderator và Admin.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Kiểm chứng:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> Tôi đối chiếu với bảng Actor–Feature của đề bài và nhận thấy một số chức năng quản trị bị AI gộp chung hoặc thiếu mức độ chi tiết cần thiết cho SRS.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Quyết định:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> Tôi giữ lại cấu trúc phân nhóm Use Case do AI đề xuất nhưng tự bổ sung các Use Case còn thiếu (Role Permission, Gamification, Chatbot Configuration, Data Export...) để đảm bảo bao phủ đầy đủ yêu cầu hệ thống.</t>
+    </r>
+  </si>
+  <si>
+    <t>Pattern Recognition + Evaluation</t>
+  </si>
+  <si>
+    <t>"Đề xuất cấu trúc thư mục ReactJS tối ưu cho dự án SEHUB có 5 role và nhiều module chức năng."</t>
+  </si>
+  <si>
+    <r>
+      <t>Phản hồi:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> AI đề xuất mô hình Feature-Based Architecture với các thư mục app, shared, features, assets và styles.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Kiểm chứng:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> Tôi so sánh với các best practices của React và nhận thấy cấu trúc AI đề xuất phù hợp cho dự án lớn, tuy nhiên một số component dùng chung và role-based layouts cần được tổ chức rõ ràng hơn để dễ mở rộng về sau.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Quyết định:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> Tôi sử dụng kiến trúc Feature-Based do AI đề xuất làm nền tảng, đồng thời chuẩn hóa thêm các thư mục layouts, hooks, context và route guards để phù hợp với yêu cầu phân quyền Guest, Student, Moderator và Admin của hệ thống SEHUB.</t>
+    </r>
   </si>
 </sst>
 </file>
@@ -158,8 +258,16 @@
     <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
-  <fonts count="22">
-    <font>
+  <fonts count="24">
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="12"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -322,6 +430,12 @@
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
     </font>
   </fonts>
   <fills count="33">
@@ -627,166 +741,173 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1172,10 +1293,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D7"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.5" outlineLevelRow="6" outlineLevelCol="3"/>
+  <dimension ref="A1:H7"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.5" outlineLevelRow="6" outlineLevelCol="7"/>
+  <cols>
+    <col min="1" max="1" width="6.33333333333333" customWidth="1"/>
+    <col min="2" max="2" width="22" customWidth="1"/>
+    <col min="3" max="3" width="23.8333333333333" customWidth="1"/>
+    <col min="4" max="4" width="84.3333333333333" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:8">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1189,7 +1316,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" ht="409.5" spans="1:4">
+    <row r="2" ht="409.5" spans="1:8">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1199,25 +1326,28 @@
       <c r="C2" t="s">
         <v>5</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="D2" s="6" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="3" ht="409.5" spans="1:4">
+      <c r="H2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" ht="409.5" spans="1:8">
       <c r="A3">
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D3" s="3" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="4" ht="409.5" spans="1:4">
+      <c r="D3" s="6" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" ht="409.5" spans="1:8">
       <c r="A4">
         <v>3</v>
       </c>
@@ -1225,52 +1355,52 @@
         <v>4</v>
       </c>
       <c r="C4" t="s">
-        <v>10</v>
-      </c>
-      <c r="D4" s="3" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="5" ht="409.5" spans="1:4">
+      <c r="D4" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="5" ht="409.5" spans="1:8">
       <c r="A5">
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C5" t="s">
-        <v>12</v>
-      </c>
-      <c r="D5" s="3" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="6" ht="409.5" spans="1:4">
+      <c r="D5" s="6" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="6" ht="409.5" spans="1:8">
       <c r="A6">
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C6" t="s">
+        <v>16</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="7" ht="409.5" spans="1:8">
+      <c r="A7" s="7">
+        <v>6</v>
+      </c>
+      <c r="B7" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="D6" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="7" ht="409.5" spans="1:4">
-      <c r="A7" s="4">
-        <v>6</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="D7" s="5" t="s">
+      <c r="C7" s="8" t="s">
         <v>18</v>
+      </c>
+      <c r="D7" s="8" t="s">
+        <v>19</v>
       </c>
     </row>
   </sheetData>
@@ -1303,106 +1433,106 @@
       </c>
     </row>
     <row r="2" ht="409.5" spans="1:4">
-      <c r="A2" s="1">
+      <c r="A2" s="4">
         <v>1</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="D2" s="2" t="s">
+      <c r="C2" s="5" t="s">
         <v>20</v>
       </c>
+      <c r="D2" s="5" t="s">
+        <v>21</v>
+      </c>
     </row>
     <row r="3" ht="409.5" spans="1:4">
-      <c r="A3" s="1">
+      <c r="A3" s="4">
         <v>2</v>
       </c>
-      <c r="B3" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="C3" s="2" t="s">
+      <c r="B3" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="C3" s="5" t="s">
         <v>23</v>
       </c>
+      <c r="D3" s="5" t="s">
+        <v>24</v>
+      </c>
     </row>
     <row r="4" ht="409.5" spans="1:4">
-      <c r="A4" s="1">
+      <c r="A4" s="4">
         <v>3</v>
       </c>
-      <c r="B4" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="D4" s="2" t="s">
+      <c r="B4" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C4" s="5" t="s">
         <v>25</v>
       </c>
+      <c r="D4" s="5" t="s">
+        <v>26</v>
+      </c>
     </row>
     <row r="5" ht="409.5" spans="1:4">
-      <c r="A5" s="1">
+      <c r="A5" s="4">
         <v>4</v>
       </c>
-      <c r="B5" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="D5" s="2" t="s">
+      <c r="B5" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C5" s="5" t="s">
         <v>27</v>
       </c>
+      <c r="D5" s="5" t="s">
+        <v>28</v>
+      </c>
     </row>
     <row r="6" ht="409.5" spans="1:4">
-      <c r="A6" s="1">
+      <c r="A6" s="4">
         <v>5</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B6" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="7" ht="409.5" spans="1:4">
+      <c r="A7" s="4">
+        <v>6</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="8" ht="409.5" spans="1:4">
+      <c r="A8" s="4">
         <v>7</v>
       </c>
-      <c r="C6" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="7" ht="409.5" spans="1:4">
-      <c r="A7" s="1">
-        <v>6</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="8" ht="409.5" spans="1:4">
-      <c r="A8" s="1">
-        <v>7</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="D8" s="2" t="s">
+      <c r="B8" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C8" s="5" t="s">
         <v>33</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="D9" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
   </sheetData>
@@ -1412,4 +1542,122 @@
     <ignoredError sqref="A9:D9" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:D11"/>
+  <sheetFormatPr defaultColWidth="8.66666666666667" defaultRowHeight="15.5" outlineLevelCol="3"/>
+  <sheetData>
+    <row r="1" customHeight="1" spans="1:4">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" ht="232.5" spans="1:4">
+      <c r="A2" s="1">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" s="1"/>
+      <c r="B3" s="1"/>
+      <c r="C3" s="1"/>
+      <c r="D3" s="3"/>
+    </row>
+    <row r="4" ht="325.5" spans="1:4">
+      <c r="A4" s="1"/>
+      <c r="B4" s="1"/>
+      <c r="C4" s="1"/>
+      <c r="D4" s="2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" s="1"/>
+      <c r="B5" s="1"/>
+      <c r="C5" s="1"/>
+      <c r="D5" s="3"/>
+    </row>
+    <row r="6" ht="409.5" customHeight="1" spans="1:4">
+      <c r="A6" s="1"/>
+      <c r="B6" s="1"/>
+      <c r="C6" s="1"/>
+      <c r="D6" s="2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="7" ht="217" spans="1:4">
+      <c r="A7" s="1">
+        <v>2</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" s="1"/>
+      <c r="B8" s="1"/>
+      <c r="C8" s="1"/>
+      <c r="D8" s="3"/>
+    </row>
+    <row r="9" ht="409.5" spans="1:4">
+      <c r="A9" s="1"/>
+      <c r="B9" s="1"/>
+      <c r="C9" s="1"/>
+      <c r="D9" s="2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" s="1"/>
+      <c r="B10" s="1"/>
+      <c r="C10" s="1"/>
+      <c r="D10" s="3"/>
+    </row>
+    <row r="11" ht="409.5" spans="1:4">
+      <c r="A11" s="1"/>
+      <c r="B11" s="1"/>
+      <c r="C11" s="1"/>
+      <c r="D11" s="2" t="s">
+        <v>45</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A2:A6"/>
+    <mergeCell ref="A7:A11"/>
+    <mergeCell ref="B2:B6"/>
+    <mergeCell ref="B7:B11"/>
+    <mergeCell ref="C2:C6"/>
+    <mergeCell ref="C7:C11"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
 </file>
--- a/AI Audit Log_NguyenVanTuanAnh.xlsx
+++ b/AI Audit Log_NguyenVanTuanAnh.xlsx
@@ -4,12 +4,13 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="7510" activeTab="2"/>
+    <workbookView windowWidth="19200" windowHeight="6910" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="Week 1" sheetId="1" r:id="rId1"/>
     <sheet name="Week 2" sheetId="2" r:id="rId2"/>
     <sheet name="Week 3" sheetId="3" r:id="rId3"/>
+    <sheet name="Week 4" sheetId="5" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -29,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="56">
   <si>
     <t>STT</t>
   </si>
@@ -159,6 +160,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>Phản hồi:</t>
     </r>
     <r>
@@ -173,6 +182,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>Kiểm chứng:</t>
     </r>
     <r>
@@ -187,6 +204,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>Quyết định:</t>
     </r>
     <r>
@@ -207,6 +232,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>Phản hồi:</t>
     </r>
     <r>
@@ -221,6 +254,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>Kiểm chứng:</t>
     </r>
     <r>
@@ -235,6 +276,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>Quyết định:</t>
     </r>
     <r>
@@ -245,6 +294,132 @@
         <charset val="134"/>
       </rPr>
       <t xml:space="preserve"> Tôi sử dụng kiến trúc Feature-Based do AI đề xuất làm nền tảng, đồng thời chuẩn hóa thêm các thư mục layouts, hooks, context và route guards để phù hợp với yêu cầu phân quyền Guest, Student, Moderator và Admin của hệ thống SEHUB.</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Routing + Layout Shell (Actor-based UI)
+</t>
+  </si>
+  <si>
+    <t>Kiểm tra phân tách giao diện Guest và Student trên khu vực /community: tab Cộng đồng, sidebar Môn học, header và layout shell.</t>
+  </si>
+  <si>
+    <r>
+      <t>Phản hồi:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> Hệ thống có 2 layout shell song song: GuestLayout + CommunityLayout (GuestHeader, FeedSidebar, CommunitySidebar) và MainLayout (MainHeader, MainSidebar, ChatFab). Route /community dùng chung CommunityLayout nhưng trước đó phụ thuộc isAuthenticated → Student đăng nhập vẫn thấy UI Guest hoặc ngược lại khi vào môn học.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Kiểm chứng:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Đối chiếu nghiệp vụ Actor (Guest xem feed công khai; Student thao tác đầy đủ trên môn học). Quy tắc đề xuất:
+/community (feed) → luôn Guest UI (CTA đăng ký, sidebar cộng đồng).
+/community/final-exam, /community/pratical-exam, /community/documents → Student UI khi đã login (MainHeader + MainSidebar).</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Quyết định:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> Phù hợp Feature-based Architecture và phân quyền theo Actor. Cần chuẩn hóa biến điều kiện showStudentShell = isAuthenticated &amp;&amp; !isFeedHome trong CommunityLayout để tránh trộn shell. Khuyến nghị bổ sung guard/route config tập trung thay vì if/else rải rác.</t>
+    </r>
+  </si>
+  <si>
+    <t>Authentication Flow + Post-login Navigation</t>
+  </si>
+  <si>
+    <t>Kiểm tra luồng đăng nhập: nút Đăng nhập trên GuestHeader, form /login, gán role user và redirect sau login thành công.</t>
+  </si>
+  <si>
+    <r>
+      <t>Phản hồi:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> Luồng auth mock nằm ở AuthProvider + LoginPage. Phát hiện 3 lỗi:
+LoginPage redirect cứng về /moderator/final-exams/add/questions cho mọi user.
+AuthProvider gán role: "moderator" cho tài khoản thường → Student bị đẩy sang khu Moderator.
+Sau login từ landing, state.from: "/" khiến user quay lại trang Guest thay vì /home.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Kiểm chứng:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Đối chiếu React Router best practices và nghiệp vụ:
+Nút Đăng nhập → /login (không auto-redirect khi đã login).
+Student login thành công → /home.
+Moderator/Admin (tài khoản test dev) → khu /moderator/*.
+Chỉ dùng from khi quay lại route protected (/home/*, /profile/*).</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Quyết định:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> Sau chỉnh sửa, luồng auth đúng Actor và UX rõ ràng. Nên tách resolvePostLoginPath() sang utils/authRedirect.js và gom role mapping vào một nguồn (tránh duplicate AuthContext.jsx / AuthProvider.jsx). Khi có API thật, thay mock bằng JWT + role từ backend.</t>
     </r>
   </si>
 </sst>
@@ -1316,7 +1491,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" ht="409.5" spans="1:8">
+    <row r="2" ht="77.5" spans="1:8">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1333,7 +1508,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" ht="409.5" spans="1:8">
+    <row r="3" ht="77.5" spans="1:8">
       <c r="A3">
         <v>2</v>
       </c>
@@ -1347,7 +1522,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" ht="409.5" spans="1:8">
+    <row r="4" ht="93" spans="1:8">
       <c r="A4">
         <v>3</v>
       </c>
@@ -1361,7 +1536,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5" ht="409.5" spans="1:8">
+    <row r="5" ht="77.5" spans="1:8">
       <c r="A5">
         <v>4</v>
       </c>
@@ -1375,7 +1550,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="6" ht="409.5" spans="1:8">
+    <row r="6" ht="62" spans="1:8">
       <c r="A6">
         <v>5</v>
       </c>
@@ -1389,7 +1564,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="7" ht="409.5" spans="1:8">
+    <row r="7" ht="72.5" spans="1:8">
       <c r="A7" s="7">
         <v>6</v>
       </c>
@@ -1660,4 +1835,122 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:D11"/>
+  <sheetFormatPr defaultColWidth="8.66666666666667" defaultRowHeight="15.5" outlineLevelCol="3"/>
+  <sheetData>
+    <row r="1" customHeight="1" spans="1:4">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" ht="409.5" spans="1:4">
+      <c r="A2" s="1">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" s="1"/>
+      <c r="B3" s="1"/>
+      <c r="C3" s="1"/>
+      <c r="D3" s="3"/>
+    </row>
+    <row r="4" ht="409.5" spans="1:4">
+      <c r="A4" s="1"/>
+      <c r="B4" s="1"/>
+      <c r="C4" s="1"/>
+      <c r="D4" s="2" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" s="1"/>
+      <c r="B5" s="1"/>
+      <c r="C5" s="1"/>
+      <c r="D5" s="3"/>
+    </row>
+    <row r="6" ht="409.5" customHeight="1" spans="1:4">
+      <c r="A6" s="1"/>
+      <c r="B6" s="1"/>
+      <c r="C6" s="1"/>
+      <c r="D6" s="2" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="7" ht="409.5" spans="1:4">
+      <c r="A7" s="1">
+        <v>2</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" s="1"/>
+      <c r="B8" s="1"/>
+      <c r="C8" s="1"/>
+      <c r="D8" s="3"/>
+    </row>
+    <row r="9" ht="409.5" spans="1:4">
+      <c r="A9" s="1"/>
+      <c r="B9" s="1"/>
+      <c r="C9" s="1"/>
+      <c r="D9" s="2" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" s="1"/>
+      <c r="B10" s="1"/>
+      <c r="C10" s="1"/>
+      <c r="D10" s="3"/>
+    </row>
+    <row r="11" ht="409.5" spans="1:4">
+      <c r="A11" s="1"/>
+      <c r="B11" s="1"/>
+      <c r="C11" s="1"/>
+      <c r="D11" s="2" t="s">
+        <v>55</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A2:A6"/>
+    <mergeCell ref="A7:A11"/>
+    <mergeCell ref="B2:B6"/>
+    <mergeCell ref="B7:B11"/>
+    <mergeCell ref="C2:C6"/>
+    <mergeCell ref="C7:C11"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
 </file>
--- a/AI Audit Log_NguyenVanTuanAnh.xlsx
+++ b/AI Audit Log_NguyenVanTuanAnh.xlsx
@@ -4,13 +4,14 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="6910" activeTab="3"/>
+    <workbookView windowWidth="19200" windowHeight="6910" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="Week 1" sheetId="1" r:id="rId1"/>
     <sheet name="Week 2" sheetId="2" r:id="rId2"/>
     <sheet name="Week 3" sheetId="3" r:id="rId3"/>
     <sheet name="Week 4" sheetId="5" r:id="rId4"/>
+    <sheet name="Week 5" sheetId="6" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="66">
   <si>
     <t>STT</t>
   </si>
@@ -305,6 +306,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>Phản hồi:</t>
     </r>
     <r>
@@ -319,6 +328,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>Kiểm chứng:</t>
     </r>
     <r>
@@ -345,6 +362,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>Quyết định:</t>
     </r>
     <r>
@@ -365,6 +390,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>Phản hồi:</t>
     </r>
     <r>
@@ -382,6 +415,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>Kiểm chứng:</t>
     </r>
     <r>
@@ -410,6 +451,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>Quyết định:</t>
     </r>
     <r>
@@ -420,6 +469,123 @@
         <charset val="134"/>
       </rPr>
       <t xml:space="preserve"> Sau chỉnh sửa, luồng auth đúng Actor và UX rõ ràng. Nên tách resolvePostLoginPath() sang utils/authRedirect.js và gom role mapping vào một nguồn (tránh duplicate AuthContext.jsx / AuthProvider.jsx). Khi có API thật, thay mock bằng JWT + role từ backend.</t>
+    </r>
+  </si>
+  <si>
+    <t>Route Guards + Phân quyền theo Actor (RBAC)</t>
+  </si>
+  <si>
+    <t>Kiểm tra lớp bảo vệ route: PrivateRoute, ModeratorRoute, AdminRoute, PremiumRoute và hook useRequireAuth — đối chiếu quyền Guest / Student / Premium / Moderator / Admin.</t>
+  </si>
+  <si>
+    <r>
+      <t>Phản hồi:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> App.jsx tổ chức route theo tầng guard rõ ràng: /home/* bọc PrivateRoute + MainLayout; /moderator/* bọc ModeratorRoute; /admin/* bọc AdminRoute; làm bài focus bọc PremiumRoute + ExamFocusLayout. Tương tác yêu cầu đăng nhập trên trang công khai dùng useRequireAuth (toast countdown → chuyển /login kèm state.from).</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Kiểm chứng:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Đối chiếu nghiệp vụ Giai đoạn 1:
+Guest truy cập /community nhưng bị chặn like/comment/tạo bài → đúng (prompt login).
+Student chưa Premium vào /exam/focus/* → redirect /home/premium → đúng.
+Student vào /admin hoặc /moderator → redirect /home → đúng.
+useRequireAuth coi /community luôn như khách (needsLoginPrompt) dù đã login → đúng với mục tiêu feed cộng đồng công khai.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Quyết định:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> Kiến trúc guard theo React Router v7 phù hợp best practice. Điểm cần cải thiện: gom logic redirect (login / premium / forbidden) vào utils/routeAccess.js; thống nhất message toast; khi có API thật, guard nên đọc role/claim từ JWT thay vì mock localStorage. Nên bổ sung test E2E cho từng guard.</t>
+    </r>
+  </si>
+  <si>
+    <t>Dual-scope Routing + Shared Feature Components</t>
+  </si>
+  <si>
+    <t>Kiểm tra mô hình route song song /home/* (Student) và /community/* (Guest) dùng chung component: ReviewQuestionsPage, PracticeQuestionsPage, DocumentsPage, SubjectDetailPage, ExamDetailPage.</t>
+  </si>
+  <si>
+    <r>
+      <t>Phản hồi:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> Cùng một feature (ôn tập, thực hành, tài liệu) được mount ở 2 namespace route:
+Student: /home/final-exam, /home/pratical-exam, /home/documents (trong PrivateRoute).
+Guest: /community/final-exam, /community/pratical-exam, /community/documents (public, CommunityLayout).
+Component dùng prop page / scope để phân biệt ngữ cảnh; sidebar SubjectNavSection trỏ URL theo scope hiện tại.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Kiểm chứng: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Đối chiếu Feature-based Architecture:
+Ưu điểm: Tái sử dụng UI/logic, tránh duplicate page; Guest khám phá nội dung trước khi đăng ký.
+Rủi ro: Drift hành vi giữa 2 scope (breadcrumb, nút làm bài, premium gate); App.jsx phình to (~230 dòng route); typo pratical-exam lặp ở cả 2 namespace.
+Exam focus: Luồng làm bài tách hẳn sang /exam/focus/* + layout riêng → tách biệt browse vs làm bài hợp lý.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Quyết định:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> Mô hình dual-scope phù hợp nghiệp vụ SEHUB (Guest preview → Student full access). Khuyến nghị: trích route config ra app/routes/ (studentRoutes, communityRoutes, adminRoutes); chuẩn hóa scope enum; sửa pratical → practice khi refactor; document rõ ma trận quyền theo từng scope trong ARCHITECTURE.md.</t>
     </r>
   </si>
 </sst>
@@ -1953,4 +2119,122 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:D11"/>
+  <sheetFormatPr defaultColWidth="8.66666666666667" defaultRowHeight="15.5" outlineLevelCol="3"/>
+  <sheetData>
+    <row r="1" customHeight="1" spans="1:4">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" ht="409.5" spans="1:4">
+      <c r="A2" s="1">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" s="1"/>
+      <c r="B3" s="1"/>
+      <c r="C3" s="1"/>
+      <c r="D3" s="3"/>
+    </row>
+    <row r="4" ht="409.5" spans="1:4">
+      <c r="A4" s="1"/>
+      <c r="B4" s="1"/>
+      <c r="C4" s="1"/>
+      <c r="D4" s="2" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" s="1"/>
+      <c r="B5" s="1"/>
+      <c r="C5" s="1"/>
+      <c r="D5" s="3"/>
+    </row>
+    <row r="6" ht="409.5" customHeight="1" spans="1:4">
+      <c r="A6" s="1"/>
+      <c r="B6" s="1"/>
+      <c r="C6" s="1"/>
+      <c r="D6" s="2" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="7" ht="409.5" spans="1:4">
+      <c r="A7" s="1">
+        <v>2</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" s="1"/>
+      <c r="B8" s="1"/>
+      <c r="C8" s="1"/>
+      <c r="D8" s="3"/>
+    </row>
+    <row r="9" ht="409.5" spans="1:4">
+      <c r="A9" s="1"/>
+      <c r="B9" s="1"/>
+      <c r="C9" s="1"/>
+      <c r="D9" s="2" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" s="1"/>
+      <c r="B10" s="1"/>
+      <c r="C10" s="1"/>
+      <c r="D10" s="3"/>
+    </row>
+    <row r="11" ht="409.5" spans="1:4">
+      <c r="A11" s="1"/>
+      <c r="B11" s="1"/>
+      <c r="C11" s="1"/>
+      <c r="D11" s="2" t="s">
+        <v>65</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A2:A6"/>
+    <mergeCell ref="A7:A11"/>
+    <mergeCell ref="B2:B6"/>
+    <mergeCell ref="B7:B11"/>
+    <mergeCell ref="C2:C6"/>
+    <mergeCell ref="C7:C11"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
 </file>
--- a/AI Audit Log_NguyenVanTuanAnh.xlsx
+++ b/AI Audit Log_NguyenVanTuanAnh.xlsx
@@ -4,14 +4,15 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="6910" activeTab="4"/>
+    <workbookView windowWidth="19200" windowHeight="7510" firstSheet="2" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="Week 1" sheetId="1" r:id="rId1"/>
     <sheet name="Week 2" sheetId="2" r:id="rId2"/>
     <sheet name="Week 3" sheetId="3" r:id="rId3"/>
-    <sheet name="Week 4" sheetId="5" r:id="rId4"/>
-    <sheet name="Week 5" sheetId="6" r:id="rId5"/>
+    <sheet name="Week 4" sheetId="4" r:id="rId4"/>
+    <sheet name="Week 5" sheetId="5" r:id="rId5"/>
+    <sheet name="Week 6" sheetId="6" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -31,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="75">
   <si>
     <t>STT</t>
   </si>
@@ -55,7 +56,7 @@
 Quyết định: Tôi giữ lại 7 module làm nền, nhưng nhận ra AI chỉ mô tả những gì nhìn thấy từ màn hình Student. Tôi quyết định bổ sung thêm 4 module ẩn (Authentication, Premium, Moderator, Admin) dựa trên yêu cầu nghiệp vụ thực tế của hệ thống.</t>
   </si>
   <si>
-    <t xml:space="preserve"> </t>
+    <t/>
   </si>
   <si>
     <t>Abstraction</t>
@@ -151,79 +152,19 @@
 Quyết định: AI không cung cấp metric cụ thể cho từng badge (vd: Active Learner = bao nhiêu ngày?). Tôi quyết định không spec đủ 26 badge trong PRO192 — chỉ định nghĩa cấu trúc 3-tier và Admin có quyền CRUD điều kiện. Thiết kế flexible, không cần deploy lại code khi điều chỉnh.</t>
   </si>
   <si>
-    <t/>
-  </si>
-  <si>
     <t>Abstraction + Decomposition</t>
   </si>
   <si>
     <t>"Dựa trên actor và feature của hệ thống SEHUB, hãy tạo toàn bộ Use Case và nhóm theo từng module chức năng."</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Phản hồi:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve"> AI liệt kê các Use Case theo nhóm Authentication, Community, Exam, Document, Premium, Moderator và Admin.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Kiểm chứng:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve"> Tôi đối chiếu với bảng Actor–Feature của đề bài và nhận thấy một số chức năng quản trị bị AI gộp chung hoặc thiếu mức độ chi tiết cần thiết cho SRS.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Quyết định:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve"> Tôi giữ lại cấu trúc phân nhóm Use Case do AI đề xuất nhưng tự bổ sung các Use Case còn thiếu (Role Permission, Gamification, Chatbot Configuration, Data Export...) để đảm bảo bao phủ đầy đủ yêu cầu hệ thống.</t>
-    </r>
+    <t>Phản hồi: AI liệt kê các Use Case theo nhóm Authentication, Community, Exam, Document, Premium, Moderator và Admin.</t>
+  </si>
+  <si>
+    <t>Kiểm chứng: Tôi đối chiếu với bảng Actor–Feature của đề bài và nhận thấy một số chức năng quản trị bị AI gộp chung hoặc thiếu mức độ chi tiết cần thiết cho SRS.</t>
+  </si>
+  <si>
+    <t>Quyết định: Tôi giữ lại cấu trúc phân nhóm Use Case do AI đề xuất nhưng tự bổ sung các Use Case còn thiếu (Role Permission, Gamification, Chatbot Configuration, Data Export...) để đảm bảo bao phủ đầy đủ yêu cầu hệ thống.</t>
   </si>
   <si>
     <t>Pattern Recognition + Evaluation</t>
@@ -232,70 +173,13 @@
     <t>"Đề xuất cấu trúc thư mục ReactJS tối ưu cho dự án SEHUB có 5 role và nhiều module chức năng."</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Phản hồi:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve"> AI đề xuất mô hình Feature-Based Architecture với các thư mục app, shared, features, assets và styles.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Kiểm chứng:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve"> Tôi so sánh với các best practices của React và nhận thấy cấu trúc AI đề xuất phù hợp cho dự án lớn, tuy nhiên một số component dùng chung và role-based layouts cần được tổ chức rõ ràng hơn để dễ mở rộng về sau.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Quyết định:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve"> Tôi sử dụng kiến trúc Feature-Based do AI đề xuất làm nền tảng, đồng thời chuẩn hóa thêm các thư mục layouts, hooks, context và route guards để phù hợp với yêu cầu phân quyền Guest, Student, Moderator và Admin của hệ thống SEHUB.</t>
-    </r>
+    <t>Phản hồi: AI đề xuất mô hình Feature-Based Architecture với các thư mục app, shared, features, assets và styles.</t>
+  </si>
+  <si>
+    <t>Kiểm chứng: Tôi so sánh với các best practices của React và nhận thấy cấu trúc AI đề xuất phù hợp cho dự án lớn, tuy nhiên một số component dùng chung và role-based layouts cần được tổ chức rõ ràng hơn để dễ mở rộng về sau.</t>
+  </si>
+  <si>
+    <t>Quyết định: Tôi sử dụng kiến trúc Feature-Based do AI đề xuất làm nền tảng, đồng thời chuẩn hóa thêm các thư mục layouts, hooks, context và route guards để phù hợp với yêu cầu phân quyền Guest, Student, Moderator và Admin của hệ thống SEHUB.</t>
   </si>
   <si>
     <t xml:space="preserve">Routing + Layout Shell (Actor-based UI)
@@ -305,82 +189,15 @@
     <t>Kiểm tra phân tách giao diện Guest và Student trên khu vực /community: tab Cộng đồng, sidebar Môn học, header và layout shell.</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Phản hồi:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve"> Hệ thống có 2 layout shell song song: GuestLayout + CommunityLayout (GuestHeader, FeedSidebar, CommunitySidebar) và MainLayout (MainHeader, MainSidebar, ChatFab). Route /community dùng chung CommunityLayout nhưng trước đó phụ thuộc isAuthenticated → Student đăng nhập vẫn thấy UI Guest hoặc ngược lại khi vào môn học.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Kiểm chứng:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Đối chiếu nghiệp vụ Actor (Guest xem feed công khai; Student thao tác đầy đủ trên môn học). Quy tắc đề xuất:
+    <t>Phản hồi: Hệ thống có 2 layout shell song song: GuestLayout + CommunityLayout (GuestHeader, FeedSidebar, CommunitySidebar) và MainLayout (MainHeader, MainSidebar, ChatFab). Route /community dùng chung CommunityLayout nhưng trước đó phụ thuộc isAuthenticated → Student đăng nhập vẫn thấy UI Guest hoặc ngược lại khi vào môn học.</t>
+  </si>
+  <si>
+    <t>Kiểm chứng: Đối chiếu nghiệp vụ Actor (Guest xem feed công khai; Student thao tác đầy đủ trên môn học). Quy tắc đề xuất:
 /community (feed) → luôn Guest UI (CTA đăng ký, sidebar cộng đồng).
 /community/final-exam, /community/pratical-exam, /community/documents → Student UI khi đã login (MainHeader + MainSidebar).</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Quyết định:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve"> Phù hợp Feature-based Architecture và phân quyền theo Actor. Cần chuẩn hóa biến điều kiện showStudentShell = isAuthenticated &amp;&amp; !isFeedHome trong CommunityLayout để tránh trộn shell. Khuyến nghị bổ sung guard/route config tập trung thay vì if/else rải rác.</t>
-    </r>
+  </si>
+  <si>
+    <t>Quyết định: Phù hợp Feature-based Architecture và phân quyền theo Actor. Cần chuẩn hóa biến điều kiện showStudentShell = isAuthenticated &amp;&amp; !isFeedHome trong CommunityLayout để tránh trộn shell. Khuyến nghị bổ sung guard/route config tập trung thay vì if/else rải rác.</t>
   </si>
   <si>
     <t>Authentication Flow + Post-login Navigation</t>
@@ -389,87 +206,20 @@
     <t>Kiểm tra luồng đăng nhập: nút Đăng nhập trên GuestHeader, form /login, gán role user và redirect sau login thành công.</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Phản hồi:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve"> Luồng auth mock nằm ở AuthProvider + LoginPage. Phát hiện 3 lỗi:
+    <t>Phản hồi: Luồng auth mock nằm ở AuthProvider + LoginPage. Phát hiện 3 lỗi:
 LoginPage redirect cứng về /moderator/final-exams/add/questions cho mọi user.
 AuthProvider gán role: "moderator" cho tài khoản thường → Student bị đẩy sang khu Moderator.
 Sau login từ landing, state.from: "/" khiến user quay lại trang Guest thay vì /home.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Kiểm chứng:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Đối chiếu React Router best practices và nghiệp vụ:
+  </si>
+  <si>
+    <t>Kiểm chứng: Đối chiếu React Router best practices và nghiệp vụ:
 Nút Đăng nhập → /login (không auto-redirect khi đã login).
 Student login thành công → /home.
 Moderator/Admin (tài khoản test dev) → khu /moderator/*.
 Chỉ dùng from khi quay lại route protected (/home/*, /profile/*).</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Quyết định:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve"> Sau chỉnh sửa, luồng auth đúng Actor và UX rõ ràng. Nên tách resolvePostLoginPath() sang utils/authRedirect.js và gom role mapping vào một nguồn (tránh duplicate AuthContext.jsx / AuthProvider.jsx). Khi có API thật, thay mock bằng JWT + role từ backend.</t>
-    </r>
+  </si>
+  <si>
+    <t>Quyết định: Sau chỉnh sửa, luồng auth đúng Actor và UX rõ ràng. Nên tách resolvePostLoginPath() sang utils/authRedirect.js và gom role mapping vào một nguồn (tránh duplicate AuthContext.jsx / AuthProvider.jsx). Khi có API thật, thay mock bằng JWT + role từ backend.</t>
   </si>
   <si>
     <t>Route Guards + Phân quyền theo Actor (RBAC)</t>
@@ -478,60 +228,17 @@
     <t>Kiểm tra lớp bảo vệ route: PrivateRoute, ModeratorRoute, AdminRoute, PremiumRoute và hook useRequireAuth — đối chiếu quyền Guest / Student / Premium / Moderator / Admin.</t>
   </si>
   <si>
-    <r>
-      <t>Phản hồi:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve"> App.jsx tổ chức route theo tầng guard rõ ràng: /home/* bọc PrivateRoute + MainLayout; /moderator/* bọc ModeratorRoute; /admin/* bọc AdminRoute; làm bài focus bọc PremiumRoute + ExamFocusLayout. Tương tác yêu cầu đăng nhập trên trang công khai dùng useRequireAuth (toast countdown → chuyển /login kèm state.from).</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Kiểm chứng:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Đối chiếu nghiệp vụ Giai đoạn 1:
+    <t>Phản hồi: App.jsx tổ chức route theo tầng guard rõ ràng: /home/* bọc PrivateRoute + MainLayout; /moderator/* bọc ModeratorRoute; /admin/* bọc AdminRoute; làm bài focus bọc PremiumRoute + ExamFocusLayout. Tương tác yêu cầu đăng nhập trên trang công khai dùng useRequireAuth (toast countdown → chuyển /login kèm state.from).</t>
+  </si>
+  <si>
+    <t>Kiểm chứng: Đối chiếu nghiệp vụ Giai đoạn 1:
 Guest truy cập /community nhưng bị chặn like/comment/tạo bài → đúng (prompt login).
 Student chưa Premium vào /exam/focus/* → redirect /home/premium → đúng.
 Student vào /admin hoặc /moderator → redirect /home → đúng.
 useRequireAuth coi /community luôn như khách (needsLoginPrompt) dù đã login → đúng với mục tiêu feed cộng đồng công khai.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Quyết định:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve"> Kiến trúc guard theo React Router v7 phù hợp best practice. Điểm cần cải thiện: gom logic redirect (login / premium / forbidden) vào utils/routeAccess.js; thống nhất message toast; khi có API thật, guard nên đọc role/claim từ JWT thay vì mock localStorage. Nên bổ sung test E2E cho từng guard.</t>
-    </r>
+  </si>
+  <si>
+    <t>Quyết định: Kiến trúc guard theo React Router v7 phù hợp best practice. Điểm cần cải thiện: gom logic redirect (login / premium / forbidden) vào utils/routeAccess.js; thống nhất message toast; khi có API thật, guard nên đọc role/claim từ JWT thay vì mock localStorage. Nên bổ sung test E2E cho từng guard.</t>
   </si>
   <si>
     <t>Dual-scope Routing + Shared Feature Components</t>
@@ -540,53 +247,56 @@
     <t>Kiểm tra mô hình route song song /home/* (Student) và /community/* (Guest) dùng chung component: ReviewQuestionsPage, PracticeQuestionsPage, DocumentsPage, SubjectDetailPage, ExamDetailPage.</t>
   </si>
   <si>
-    <r>
-      <t>Phản hồi:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve"> Cùng một feature (ôn tập, thực hành, tài liệu) được mount ở 2 namespace route:
+    <t>Phản hồi: Cùng một feature (ôn tập, thực hành, tài liệu) được mount ở 2 namespace route:
 Student: /home/final-exam, /home/pratical-exam, /home/documents (trong PrivateRoute).
 Guest: /community/final-exam, /community/pratical-exam, /community/documents (public, CommunityLayout).
 Component dùng prop page / scope để phân biệt ngữ cảnh; sidebar SubjectNavSection trỏ URL theo scope hiện tại.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Kiểm chứng: </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Đối chiếu Feature-based Architecture:
+  </si>
+  <si>
+    <t>Kiểm chứng: Đối chiếu Feature-based Architecture:
 Ưu điểm: Tái sử dụng UI/logic, tránh duplicate page; Guest khám phá nội dung trước khi đăng ký.
 Rủi ro: Drift hành vi giữa 2 scope (breadcrumb, nút làm bài, premium gate); App.jsx phình to (~230 dòng route); typo pratical-exam lặp ở cả 2 namespace.
 Exam focus: Luồng làm bài tách hẳn sang /exam/focus/* + layout riêng → tách biệt browse vs làm bài hợp lý.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Quyết định:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve"> Mô hình dual-scope phù hợp nghiệp vụ SEHUB (Guest preview → Student full access). Khuyến nghị: trích route config ra app/routes/ (studentRoutes, communityRoutes, adminRoutes); chuẩn hóa scope enum; sửa pratical → practice khi refactor; document rõ ma trận quyền theo từng scope trong ARCHITECTURE.md.</t>
-    </r>
+  </si>
+  <si>
+    <t>Quyết định: Mô hình dual-scope phù hợp nghiệp vụ SEHUB (Guest preview → Student full access). Khuyến nghị: trích route config ra app/routes/ (studentRoutes, communityRoutes, adminRoutes); chuẩn hóa scope enum; sửa pratical → practice khi refactor; document rõ ma trận quyền theo từng scope trong ARCHITECTURE.md.</t>
+  </si>
+  <si>
+    <t>Theme Persistence + Anti-FOUC</t>
+  </si>
+  <si>
+    <t>Kiểm tra cơ chế dark/light mode của SEHUB: bootstrap theme trước khi React hydrate, lưu preference light/dark/system, và áp dụng data-theme lên documentElement.</t>
+  </si>
+  <si>
+    <t>Phản hồi: Theme bootstrap nằm trong fe/index.html — script đọc localStorage["sehub-theme"] và gán document.documentElement.dataset.theme trước khi bundle React chạy, tránh FOUC (flash of wrong theme). Logic đọc/ghi/resolve nằm ở utils/themeStorage.js; ThemeProvider.jsx bọc app, lắng nghe prefers-color-scheme khi preference = system. Hook useTheme / useThemeOptional cung cấp theme đã resolve cho component.</t>
+  </si>
+  <si>
+    <t>Kiểm chứng: Đối chiếu UX dark mode hiện đại:
+Preference 3 trạng thái (light | dark | system) đúng nhu cầu — system theo OS.
+Anti-FOUC script trong index.html là bắt buộc với SPA Vite; nếu chỉ set theme trong useEffect sẽ nháy sáng khi reload.
+Key localStorage "sehub-theme" nhất quán với applyTheme trên &lt;html data-theme="..."&gt;.
+useThemeOptional tránh crash khi chart/header render ngoài ThemeProvider (edge case test).</t>
+  </si>
+  <si>
+    <t>Quyết định: Giữ kiến trúc themeStorage + ThemeProvider + early bootstrap. Không dùng class .dark kiểu Tailwind vì SEHUB dùng CSS Modules + CSS variables. Persist preference (không chỉ resolved theme) để system vẫn theo OS khi user đổi chế độ máy. Document rõ: đổi theme = đổi dataset.theme, toàn bộ token trong variables.css tự cập nhật.</t>
+  </si>
+  <si>
+    <t>Design Tokens + ThemeSwitcher UI</t>
+  </si>
+  <si>
+    <t>Triển khai token màu light/dark trong variables.css và gắn ThemeSwitcher vào GuestHeader, MainHeader, AdminHeader, ModeratorHeader để mọi actor đều đổi theme được.</t>
+  </si>
+  <si>
+    <t>Phản hồi: variables.css định nghĩa :root (light) và [data-theme="dark"] với bộ --color-*, shadow, feed background, auth gradient. ThemeSwitcher hỗ trợ compact (header hẹp) và menu (dropdown). Gắn vào GuestHeader, HeaderUserActions (Student), AdminHeader, ModeratorHeader — đủ 4 shell actor.</t>
+  </si>
+  <si>
+    <t>Kiểm chứng: Token-first đúng hướng — đổi theme không cần sửa từng page nếu dùng var(--color-*).
+Một số trang vẫn còn hex cứng + override [data-theme="dark"] cục bộ (status chip, moderation) → chưa 100% token-only.
+ThemeSwitcher compact cần trên mobile Guest để không chiếm chỗ nav.
+Thiếu switcher ở một header = actor đó không đổi theme được → phải cover đủ 4 header.</t>
+  </si>
+  <si>
+    <t>Quyết định: Chuẩn hóa token trong variables.css làm nguồn sự thật; ThemeSwitcher bắt buộc trên mọi header shell. Override [data-theme="dark"] chỉ chấp nhận cho màu ngữ nghĩa (success/warning/danger chip) khi chưa có token riêng. Backlog: dần thay hex cứng còn lại bằng CSS variables để giảm duplicate màu giữa light/dark.</t>
   </si>
 </sst>
 </file>
@@ -599,13 +309,24 @@
     <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
-  <fonts count="24">
+  <fonts count="25">
     <font>
       <sz val="12"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
     </font>
     <font>
       <b/>
@@ -771,12 +492,6 @@
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
     </font>
   </fonts>
   <fills count="33">
@@ -1082,173 +797,169 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="176" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="7">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="6" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="7" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="8" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="9" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="10" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="11" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="12" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="13" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="14" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="15" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="16" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="17" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="18" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="19" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="20" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="22" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="23" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="24" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="25" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="26" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="27" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="28" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="29" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="30" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="31" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="32" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+  <cellXfs count="7">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1657,7 +1368,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" ht="77.5" spans="1:8">
+    <row r="2" ht="77.5" customHeight="1" spans="1:8">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1667,14 +1378,14 @@
       <c r="C2" t="s">
         <v>5</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="D2" s="3" t="s">
         <v>6</v>
       </c>
       <c r="H2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="3" ht="77.5" spans="1:8">
+    <row r="3" ht="77.5" customHeight="1" spans="1:8">
       <c r="A3">
         <v>2</v>
       </c>
@@ -1684,11 +1395,11 @@
       <c r="C3" t="s">
         <v>9</v>
       </c>
-      <c r="D3" s="6" t="s">
+      <c r="D3" s="3" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="4" ht="93" spans="1:8">
+    <row r="4" ht="93" customHeight="1" spans="1:8">
       <c r="A4">
         <v>3</v>
       </c>
@@ -1698,11 +1409,11 @@
       <c r="C4" t="s">
         <v>11</v>
       </c>
-      <c r="D4" s="6" t="s">
+      <c r="D4" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="5" ht="77.5" spans="1:8">
+    <row r="5" ht="77.5" customHeight="1" spans="1:8">
       <c r="A5">
         <v>4</v>
       </c>
@@ -1712,11 +1423,11 @@
       <c r="C5" t="s">
         <v>13</v>
       </c>
-      <c r="D5" s="6" t="s">
+      <c r="D5" s="3" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="6" ht="62" spans="1:8">
+    <row r="6" ht="62" customHeight="1" spans="1:8">
       <c r="A6">
         <v>5</v>
       </c>
@@ -1726,30 +1437,27 @@
       <c r="C6" t="s">
         <v>16</v>
       </c>
-      <c r="D6" s="6" t="s">
+      <c r="D6" s="3" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="7" ht="72.5" spans="1:8">
-      <c r="A7" s="7">
+    <row r="7" ht="72.5" customHeight="1" spans="1:8">
+      <c r="A7" s="5">
         <v>6</v>
       </c>
-      <c r="B7" s="8" t="s">
+      <c r="B7" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="C7" s="8" t="s">
+      <c r="C7" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="D7" s="8" t="s">
+      <c r="D7" s="6" t="s">
         <v>19</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
-  <ignoredErrors>
-    <ignoredError sqref="A1:D1" numberStoredAsText="1"/>
-  </ignoredErrors>
 </worksheet>
 </file>
 
@@ -1773,115 +1481,112 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" ht="409.5" spans="1:4">
-      <c r="A2" s="4">
+    <row r="2" ht="409.5" customHeight="1" spans="1:4">
+      <c r="A2" s="5">
         <v>1</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="C2" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="D2" s="6" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="3" ht="409.5" spans="1:4">
-      <c r="A3" s="4">
+    <row r="3" ht="409.5" customHeight="1" spans="1:4">
+      <c r="A3" s="5">
         <v>2</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="C3" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="D3" s="5" t="s">
+      <c r="D3" s="6" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="4" ht="409.5" spans="1:4">
-      <c r="A4" s="4">
+    <row r="4" ht="409.5" customHeight="1" spans="1:4">
+      <c r="A4" s="5">
         <v>3</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="B4" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="C4" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="D4" s="5" t="s">
+      <c r="D4" s="6" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="5" ht="409.5" spans="1:4">
-      <c r="A5" s="4">
+    <row r="5" ht="409.5" customHeight="1" spans="1:4">
+      <c r="A5" s="5">
         <v>4</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="B5" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="C5" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="D5" s="5" t="s">
+      <c r="D5" s="6" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="6" ht="409.5" spans="1:4">
-      <c r="A6" s="4">
+    <row r="6" ht="409.5" customHeight="1" spans="1:4">
+      <c r="A6" s="5">
         <v>5</v>
       </c>
-      <c r="B6" s="5" t="s">
+      <c r="B6" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="C6" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="D6" s="5" t="s">
+      <c r="D6" s="6" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="7" ht="409.5" spans="1:4">
-      <c r="A7" s="4">
+    <row r="7" ht="409.5" customHeight="1" spans="1:4">
+      <c r="A7" s="5">
         <v>6</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B7" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="C7" s="5" t="s">
+      <c r="C7" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="D7" s="5" t="s">
+      <c r="D7" s="6" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="8" ht="409.5" spans="1:4">
-      <c r="A8" s="4">
+    <row r="8" ht="409.5" customHeight="1" spans="1:4">
+      <c r="A8" s="5">
         <v>7</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="B8" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="C8" s="5" t="s">
+      <c r="C8" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="D8" s="5" t="s">
+      <c r="D8" s="6" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="D9" t="s">
-        <v>35</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
-  <ignoredErrors>
-    <ignoredError sqref="A9:D9" numberStoredAsText="1"/>
-  </ignoredErrors>
 </worksheet>
 </file>
 
@@ -1891,7 +1596,7 @@
   <dimension ref="A1:D11"/>
   <sheetFormatPr defaultColWidth="8.66666666666667" defaultRowHeight="15.5" outlineLevelCol="3"/>
   <sheetData>
-    <row r="1" customHeight="1" spans="1:4">
+    <row r="1" spans="1:4">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1905,88 +1610,52 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" ht="232.5" spans="1:4">
-      <c r="A2" s="1">
+    <row r="2" ht="232.5" customHeight="1" spans="1:4">
+      <c r="A2" s="3">
         <v>1</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="C2" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="D2" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="D2" s="2" t="s">
+    </row>
+    <row r="4" ht="325.5" customHeight="1" spans="1:4">
+      <c r="D4" s="4" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="3" spans="1:4">
-      <c r="A3" s="1"/>
-      <c r="B3" s="1"/>
-      <c r="C3" s="1"/>
-      <c r="D3" s="3"/>
-    </row>
-    <row r="4" ht="325.5" spans="1:4">
-      <c r="A4" s="1"/>
-      <c r="B4" s="1"/>
-      <c r="C4" s="1"/>
-      <c r="D4" s="2" t="s">
+    <row r="6" ht="409.5" customHeight="1" spans="1:4">
+      <c r="D6" s="4" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="5" spans="1:4">
-      <c r="A5" s="1"/>
-      <c r="B5" s="1"/>
-      <c r="C5" s="1"/>
-      <c r="D5" s="3"/>
-    </row>
-    <row r="6" ht="409.5" customHeight="1" spans="1:4">
-      <c r="A6" s="1"/>
-      <c r="B6" s="1"/>
-      <c r="C6" s="1"/>
-      <c r="D6" s="2" t="s">
+    <row r="7" ht="217" customHeight="1" spans="1:4">
+      <c r="A7" s="3">
+        <v>2</v>
+      </c>
+      <c r="B7" s="3" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="7" ht="217" spans="1:4">
-      <c r="A7" s="1">
-        <v>2</v>
-      </c>
-      <c r="B7" s="1" t="s">
+      <c r="C7" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="C7" s="1" t="s">
+      <c r="D7" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="D7" s="2" t="s">
+    </row>
+    <row r="9" ht="409.5" customHeight="1" spans="1:4">
+      <c r="D9" s="4" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="8" spans="1:4">
-      <c r="A8" s="1"/>
-      <c r="B8" s="1"/>
-      <c r="C8" s="1"/>
-      <c r="D8" s="3"/>
-    </row>
-    <row r="9" ht="409.5" spans="1:4">
-      <c r="A9" s="1"/>
-      <c r="B9" s="1"/>
-      <c r="C9" s="1"/>
-      <c r="D9" s="2" t="s">
+    <row r="11" ht="409.5" customHeight="1" spans="1:4">
+      <c r="D11" s="4" t="s">
         <v>44</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4">
-      <c r="A10" s="1"/>
-      <c r="B10" s="1"/>
-      <c r="C10" s="1"/>
-      <c r="D10" s="3"/>
-    </row>
-    <row r="11" ht="409.5" spans="1:4">
-      <c r="A11" s="1"/>
-      <c r="B11" s="1"/>
-      <c r="C11" s="1"/>
-      <c r="D11" s="2" t="s">
-        <v>45</v>
       </c>
     </row>
   </sheetData>
@@ -2009,7 +1678,7 @@
   <dimension ref="A1:D11"/>
   <sheetFormatPr defaultColWidth="8.66666666666667" defaultRowHeight="15.5" outlineLevelCol="3"/>
   <sheetData>
-    <row r="1" customHeight="1" spans="1:4">
+    <row r="1" spans="1:4">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2023,88 +1692,52 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" ht="409.5" spans="1:4">
-      <c r="A2" s="1">
+    <row r="2" ht="409.5" customHeight="1" spans="1:4">
+      <c r="A2" s="3">
         <v>1</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="C2" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="D2" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="D2" s="2" t="s">
+    </row>
+    <row r="4" ht="409.5" customHeight="1" spans="1:4">
+      <c r="D4" s="4" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="3" spans="1:4">
-      <c r="A3" s="1"/>
-      <c r="B3" s="1"/>
-      <c r="C3" s="1"/>
-      <c r="D3" s="3"/>
-    </row>
-    <row r="4" ht="409.5" spans="1:4">
-      <c r="A4" s="1"/>
-      <c r="B4" s="1"/>
-      <c r="C4" s="1"/>
-      <c r="D4" s="2" t="s">
+    <row r="6" ht="409.5" customHeight="1" spans="1:4">
+      <c r="D6" s="4" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="5" spans="1:4">
-      <c r="A5" s="1"/>
-      <c r="B5" s="1"/>
-      <c r="C5" s="1"/>
-      <c r="D5" s="3"/>
-    </row>
-    <row r="6" ht="409.5" customHeight="1" spans="1:4">
-      <c r="A6" s="1"/>
-      <c r="B6" s="1"/>
-      <c r="C6" s="1"/>
-      <c r="D6" s="2" t="s">
+    <row r="7" ht="409.5" customHeight="1" spans="1:4">
+      <c r="A7" s="3">
+        <v>2</v>
+      </c>
+      <c r="B7" s="3" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="7" ht="409.5" spans="1:4">
-      <c r="A7" s="1">
-        <v>2</v>
-      </c>
-      <c r="B7" s="1" t="s">
+      <c r="C7" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="C7" s="1" t="s">
+      <c r="D7" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="D7" s="2" t="s">
+    </row>
+    <row r="9" ht="409.5" customHeight="1" spans="1:4">
+      <c r="D9" s="4" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="8" spans="1:4">
-      <c r="A8" s="1"/>
-      <c r="B8" s="1"/>
-      <c r="C8" s="1"/>
-      <c r="D8" s="3"/>
-    </row>
-    <row r="9" ht="409.5" spans="1:4">
-      <c r="A9" s="1"/>
-      <c r="B9" s="1"/>
-      <c r="C9" s="1"/>
-      <c r="D9" s="2" t="s">
+    <row r="11" ht="409.5" customHeight="1" spans="1:4">
+      <c r="D11" s="4" t="s">
         <v>54</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4">
-      <c r="A10" s="1"/>
-      <c r="B10" s="1"/>
-      <c r="C10" s="1"/>
-      <c r="D10" s="3"/>
-    </row>
-    <row r="11" ht="409.5" spans="1:4">
-      <c r="A11" s="1"/>
-      <c r="B11" s="1"/>
-      <c r="C11" s="1"/>
-      <c r="D11" s="2" t="s">
-        <v>55</v>
       </c>
     </row>
   </sheetData>
@@ -2127,7 +1760,7 @@
   <dimension ref="A1:D11"/>
   <sheetFormatPr defaultColWidth="8.66666666666667" defaultRowHeight="15.5" outlineLevelCol="3"/>
   <sheetData>
-    <row r="1" customHeight="1" spans="1:4">
+    <row r="1" spans="1:4">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2141,88 +1774,134 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" ht="409.5" spans="1:4">
+    <row r="2" ht="409.5" customHeight="1" spans="1:4">
+      <c r="A2" s="3">
+        <v>1</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="4" ht="409.5" customHeight="1" spans="1:4">
+      <c r="D4" s="4" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="6" ht="409.5" customHeight="1" spans="1:4">
+      <c r="D6" s="4" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="7" ht="409.5" customHeight="1" spans="1:4">
+      <c r="A7" s="3">
+        <v>2</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="9" ht="409.5" customHeight="1" spans="1:4">
+      <c r="D9" s="4" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="11" ht="409.5" customHeight="1" spans="1:4">
+      <c r="D11" s="4" t="s">
+        <v>64</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A2:A6"/>
+    <mergeCell ref="A7:A11"/>
+    <mergeCell ref="B2:B6"/>
+    <mergeCell ref="B7:B11"/>
+    <mergeCell ref="C2:C6"/>
+    <mergeCell ref="C7:C11"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:D11"/>
+  <sheetFormatPr defaultColWidth="8.66666666666667" defaultRowHeight="15.5" outlineLevelCol="3"/>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" ht="409.5" customHeight="1" spans="1:4">
       <c r="A2" s="1">
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>57</v>
+        <v>66</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4">
-      <c r="A3" s="1"/>
-      <c r="B3" s="1"/>
-      <c r="C3" s="1"/>
-      <c r="D3" s="3"/>
-    </row>
-    <row r="4" ht="409.5" spans="1:4">
-      <c r="A4" s="1"/>
-      <c r="B4" s="1"/>
-      <c r="C4" s="1"/>
+        <v>67</v>
+      </c>
+    </row>
+    <row r="4" ht="409.5" customHeight="1" spans="1:4">
       <c r="D4" s="2" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4">
-      <c r="A5" s="1"/>
-      <c r="B5" s="1"/>
-      <c r="C5" s="1"/>
-      <c r="D5" s="3"/>
+        <v>68</v>
+      </c>
     </row>
     <row r="6" ht="409.5" customHeight="1" spans="1:4">
-      <c r="A6" s="1"/>
-      <c r="B6" s="1"/>
-      <c r="C6" s="1"/>
       <c r="D6" s="2" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="7" ht="409.5" spans="1:4">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="7" ht="409.5" customHeight="1" spans="1:4">
       <c r="A7" s="1">
         <v>2</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>61</v>
+        <v>70</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>62</v>
+        <v>71</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4">
-      <c r="A8" s="1"/>
-      <c r="B8" s="1"/>
-      <c r="C8" s="1"/>
-      <c r="D8" s="3"/>
-    </row>
-    <row r="9" ht="409.5" spans="1:4">
-      <c r="A9" s="1"/>
-      <c r="B9" s="1"/>
-      <c r="C9" s="1"/>
+        <v>72</v>
+      </c>
+    </row>
+    <row r="9" ht="409.5" customHeight="1" spans="1:4">
       <c r="D9" s="2" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4">
-      <c r="A10" s="1"/>
-      <c r="B10" s="1"/>
-      <c r="C10" s="1"/>
-      <c r="D10" s="3"/>
-    </row>
-    <row r="11" ht="409.5" spans="1:4">
-      <c r="A11" s="1"/>
-      <c r="B11" s="1"/>
-      <c r="C11" s="1"/>
+        <v>73</v>
+      </c>
+    </row>
+    <row r="11" ht="409.5" customHeight="1" spans="1:4">
       <c r="D11" s="2" t="s">
-        <v>65</v>
+        <v>74</v>
       </c>
     </row>
   </sheetData>

--- a/AI Audit Log_NguyenVanTuanAnh.xlsx
+++ b/AI Audit Log_NguyenVanTuanAnh.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="7510" firstSheet="2" activeTab="5"/>
+    <workbookView windowWidth="19200" windowHeight="7510" firstSheet="2" activeTab="6"/>
   </bookViews>
   <sheets>
     <sheet name="Week 1" sheetId="1" r:id="rId1"/>
@@ -13,6 +13,7 @@
     <sheet name="Week 4" sheetId="4" r:id="rId4"/>
     <sheet name="Week 5" sheetId="5" r:id="rId5"/>
     <sheet name="Week 6" sheetId="6" r:id="rId6"/>
+    <sheet name="Week 7" sheetId="7" r:id="rId7"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -32,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="85">
   <si>
     <t>STT</t>
   </si>
@@ -297,6 +298,42 @@
   </si>
   <si>
     <t>Quyết định: Chuẩn hóa token trong variables.css làm nguồn sự thật; ThemeSwitcher bắt buộc trên mọi header shell. Override [data-theme="dark"] chỉ chấp nhận cho màu ngữ nghĩa (success/warning/danger chip) khi chưa có token riêng. Backlog: dần thay hex cứng còn lại bằng CSS variables để giảm duplicate màu giữa light/dark.</t>
+  </si>
+  <si>
+    <t>Chart Theme theo Dark Mode</t>
+  </si>
+  <si>
+    <t>Đồng bộ màu biểu đồ Admin dashboard (Recharts) với theme hiện tại: tách chartTheme, dùng useThemeOptional, remount chart khi đổi theme để tránh màu cũ bị giữ.</t>
+  </si>
+  <si>
+    <t>Phản hồi: AI đề xuất file features/admin/dashboard/charts/chartTheme.js map màu axis/grid/tooltip/series theo light|dark. Chart dùng useThemeOptional() lấy resolved theme; key={theme} trên ResponsiveContainer/Chart để Recharts remount khi đổi theme (tránh state màu cũ). ChartResponsiveContainer.jsx bọc chung các chart admin.</t>
+  </si>
+  <si>
+    <t>Kiểm chứng: Recharts không tự đọc CSS variables cho mọi prop (stroke, fill) → cần JS theme map, không chỉ CSS.
+Remount bằng key={theme} đơn giản, đáng tin hơn cố patch từng Series.
+useThemeOptional an toàn hơn useTheme nếu chart render trong Suspense/test thiếu Provider.
+Cần kiểm tra contrast tooltip/legend trên nền dark (đọc được, không lẫn grid).</t>
+  </si>
+  <si>
+    <t>Quyết định: Giữ chartTheme.js + remount theo theme. Không nhúng màu chart vào CSS Modules từng page (dễ lệch token). Mọi chart admin mới phải import chartTheme thay vì hardcode hex. Có thể mở rộng token chart vào variables.css sau nếu muốn đồng bộ design system chặt hơn.</t>
+  </si>
+  <si>
+    <t>Loại bỏ màu cứng trùng lặp (Dark CSS)</t>
+  </si>
+  <si>
+    <t>Rà soát các file CSS còn hardcode màu hex cho dark mode; chuyển sang CSS variables hoặc khối [data-theme="dark"] thống nhất, giảm duplicate giữa trang Admin/Moderator/Community.</t>
+  </si>
+  <si>
+    <t>Phản hồi: Sau theme nền, ~20+ file CSS vẫn có [data-theme="dark"] hoặc hex riêng (status badge, feed card, moderation queue). AI đề xuất ưu tiên map sang --color-* đã có; chỉ giữ override khi màu ngữ nghĩa chưa có token (ví dụ chip Pending/Approved khác nhau).</t>
+  </si>
+  <si>
+    <t>Kiểm chứng: Duplicate màu gây lệch UX — cùng "nền card" nhưng hex khác nhau giữa Admin và Moderator khi dark.
+Chuyển hết sang token giảm chi phí maintain khi đổi palette.
+Rủi ro: thay ồ ạt dễ phá contrast từng trang → nên làm theo nhóm (shell → shared badge → page-specific).
+Git history (follow-up dark CSS sau commit theme) xác nhận đây là phase polish, không phải foundation.</t>
+  </si>
+  <si>
+    <t>Quyết định: Chiến lược 2 tầng — (1) token global trong variables.css, (2) override cục bộ có kiểm soát cho status/moderation. Không xóa hết [data-theme="dark"] page-level trong một PR lớn; refactor từng cụm shared (badge, table, card) trước. Mục tiêu: giảm hex trùng, không phá visual đã QA.</t>
   </si>
 </sst>
 </file>
@@ -309,10 +346,23 @@
     <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
-  <fonts count="25">
+  <fonts count="27">
     <font>
       <sz val="12"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
       <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -797,28 +847,19 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="176" fontId="5" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="5" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="5" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="5" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="5" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1">
+    <xf numFmtId="176" fontId="7" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="7" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="7" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="7" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
@@ -827,122 +868,131 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="2">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="6">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="7">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="6" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="7" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="8" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="9" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="10" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="11" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="12" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="13" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="14" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="15" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="16" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="17" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="18" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="19" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="20" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="21" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="22" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="23" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="24" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="25" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="26" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="27" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="28" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="29" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="30" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="31" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="32" borderId="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="2">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="5" borderId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="7">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="8">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="6" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="7" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="8" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="9" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="10" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="11" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="12" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="13" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="14" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="15" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="16" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="17" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="18" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="19" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="20" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="21" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="22" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="23" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="24" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="25" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="26" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="27" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="28" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="29" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="30" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="31" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="32" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -950,16 +1000,22 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1378,7 +1434,7 @@
       <c r="C2" t="s">
         <v>5</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="D2" s="5" t="s">
         <v>6</v>
       </c>
       <c r="H2" t="s">
@@ -1395,7 +1451,7 @@
       <c r="C3" t="s">
         <v>9</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="D3" s="5" t="s">
         <v>10</v>
       </c>
     </row>
@@ -1409,7 +1465,7 @@
       <c r="C4" t="s">
         <v>11</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="D4" s="5" t="s">
         <v>12</v>
       </c>
     </row>
@@ -1423,7 +1479,7 @@
       <c r="C5" t="s">
         <v>13</v>
       </c>
-      <c r="D5" s="3" t="s">
+      <c r="D5" s="5" t="s">
         <v>14</v>
       </c>
     </row>
@@ -1437,21 +1493,21 @@
       <c r="C6" t="s">
         <v>16</v>
       </c>
-      <c r="D6" s="3" t="s">
+      <c r="D6" s="5" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="7" ht="72.5" customHeight="1" spans="1:8">
-      <c r="A7" s="5">
+      <c r="A7" s="7">
         <v>6</v>
       </c>
-      <c r="B7" s="6" t="s">
+      <c r="B7" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="C7" s="6" t="s">
+      <c r="C7" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="D7" s="6" t="s">
+      <c r="D7" s="8" t="s">
         <v>19</v>
       </c>
     </row>
@@ -1482,100 +1538,100 @@
       </c>
     </row>
     <row r="2" ht="409.5" customHeight="1" spans="1:4">
-      <c r="A2" s="5">
+      <c r="A2" s="7">
         <v>1</v>
       </c>
-      <c r="B2" s="6" t="s">
+      <c r="B2" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="6" t="s">
+      <c r="C2" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="D2" s="8" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="3" ht="409.5" customHeight="1" spans="1:4">
-      <c r="A3" s="5">
+      <c r="A3" s="7">
         <v>2</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="B3" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="C3" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="D3" s="6" t="s">
+      <c r="D3" s="8" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="4" ht="409.5" customHeight="1" spans="1:4">
-      <c r="A4" s="5">
+      <c r="A4" s="7">
         <v>3</v>
       </c>
-      <c r="B4" s="6" t="s">
+      <c r="B4" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="C4" s="6" t="s">
+      <c r="C4" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="D4" s="6" t="s">
+      <c r="D4" s="8" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="5" ht="409.5" customHeight="1" spans="1:4">
-      <c r="A5" s="5">
+      <c r="A5" s="7">
         <v>4</v>
       </c>
-      <c r="B5" s="6" t="s">
+      <c r="B5" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="C5" s="6" t="s">
+      <c r="C5" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="D5" s="6" t="s">
+      <c r="D5" s="8" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="6" ht="409.5" customHeight="1" spans="1:4">
-      <c r="A6" s="5">
+      <c r="A6" s="7">
         <v>5</v>
       </c>
-      <c r="B6" s="6" t="s">
+      <c r="B6" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="C6" s="6" t="s">
+      <c r="C6" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="D6" s="6" t="s">
+      <c r="D6" s="8" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="7" ht="409.5" customHeight="1" spans="1:4">
-      <c r="A7" s="5">
+      <c r="A7" s="7">
         <v>6</v>
       </c>
-      <c r="B7" s="6" t="s">
+      <c r="B7" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="C7" s="6" t="s">
+      <c r="C7" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="D7" s="6" t="s">
+      <c r="D7" s="8" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="8" ht="409.5" customHeight="1" spans="1:4">
-      <c r="A8" s="5">
+      <c r="A8" s="7">
         <v>7</v>
       </c>
-      <c r="B8" s="6" t="s">
+      <c r="B8" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="C8" s="6" t="s">
+      <c r="C8" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="D8" s="6" t="s">
+      <c r="D8" s="8" t="s">
         <v>34</v>
       </c>
     </row>
@@ -1611,50 +1667,50 @@
       </c>
     </row>
     <row r="2" ht="232.5" customHeight="1" spans="1:4">
-      <c r="A2" s="3">
+      <c r="A2" s="5">
         <v>1</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="D2" s="6" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="4" ht="325.5" customHeight="1" spans="1:4">
-      <c r="D4" s="4" t="s">
+      <c r="D4" s="6" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="6" ht="409.5" customHeight="1" spans="1:4">
-      <c r="D6" s="4" t="s">
+      <c r="D6" s="6" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="7" ht="217" customHeight="1" spans="1:4">
-      <c r="A7" s="3">
+      <c r="A7" s="5">
         <v>2</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B7" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="C7" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="D7" s="4" t="s">
+      <c r="D7" s="6" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="9" ht="409.5" customHeight="1" spans="1:4">
-      <c r="D9" s="4" t="s">
+      <c r="D9" s="6" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="11" ht="409.5" customHeight="1" spans="1:4">
-      <c r="D11" s="4" t="s">
+      <c r="D11" s="6" t="s">
         <v>44</v>
       </c>
     </row>
@@ -1693,50 +1749,50 @@
       </c>
     </row>
     <row r="2" ht="409.5" customHeight="1" spans="1:4">
-      <c r="A2" s="3">
+      <c r="A2" s="5">
         <v>1</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="D2" s="6" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="4" ht="409.5" customHeight="1" spans="1:4">
-      <c r="D4" s="4" t="s">
+      <c r="D4" s="6" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="6" ht="409.5" customHeight="1" spans="1:4">
-      <c r="D6" s="4" t="s">
+      <c r="D6" s="6" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="7" ht="409.5" customHeight="1" spans="1:4">
-      <c r="A7" s="3">
+      <c r="A7" s="5">
         <v>2</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B7" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="C7" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="D7" s="4" t="s">
+      <c r="D7" s="6" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="9" ht="409.5" customHeight="1" spans="1:4">
-      <c r="D9" s="4" t="s">
+      <c r="D9" s="6" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="11" ht="409.5" customHeight="1" spans="1:4">
-      <c r="D11" s="4" t="s">
+      <c r="D11" s="6" t="s">
         <v>54</v>
       </c>
     </row>
@@ -1775,50 +1831,50 @@
       </c>
     </row>
     <row r="2" ht="409.5" customHeight="1" spans="1:4">
-      <c r="A2" s="3">
+      <c r="A2" s="5">
         <v>1</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="D2" s="6" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="4" ht="409.5" customHeight="1" spans="1:4">
-      <c r="D4" s="4" t="s">
+      <c r="D4" s="6" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="6" ht="409.5" customHeight="1" spans="1:4">
-      <c r="D6" s="4" t="s">
+      <c r="D6" s="6" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="7" ht="409.5" customHeight="1" spans="1:4">
-      <c r="A7" s="3">
+      <c r="A7" s="5">
         <v>2</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B7" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="C7" s="5" t="s">
         <v>61</v>
       </c>
-      <c r="D7" s="4" t="s">
+      <c r="D7" s="6" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="9" ht="409.5" customHeight="1" spans="1:4">
-      <c r="D9" s="4" t="s">
+      <c r="D9" s="6" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="11" ht="409.5" customHeight="1" spans="1:4">
-      <c r="D11" s="4" t="s">
+      <c r="D11" s="6" t="s">
         <v>64</v>
       </c>
     </row>
@@ -1857,51 +1913,133 @@
       </c>
     </row>
     <row r="2" ht="409.5" customHeight="1" spans="1:4">
+      <c r="A2" s="3">
+        <v>1</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="4" ht="409.5" customHeight="1" spans="1:4">
+      <c r="D4" s="4" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="6" ht="409.5" customHeight="1" spans="1:4">
+      <c r="D6" s="4" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="7" ht="409.5" customHeight="1" spans="1:4">
+      <c r="A7" s="3">
+        <v>2</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="9" ht="409.5" customHeight="1" spans="1:4">
+      <c r="D9" s="4" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="11" ht="409.5" customHeight="1" spans="1:4">
+      <c r="D11" s="4" t="s">
+        <v>74</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A2:A6"/>
+    <mergeCell ref="A7:A11"/>
+    <mergeCell ref="B2:B6"/>
+    <mergeCell ref="B7:B11"/>
+    <mergeCell ref="C2:C6"/>
+    <mergeCell ref="C7:C11"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:D11"/>
+  <sheetFormatPr defaultColWidth="8.66666666666667" defaultRowHeight="15.5" outlineLevelCol="3"/>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" ht="409.5" spans="1:4">
       <c r="A2" s="1">
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>66</v>
+        <v>76</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="4" ht="409.5" customHeight="1" spans="1:4">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="4" ht="409.5" spans="1:4">
       <c r="D4" s="2" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="6" ht="409.5" customHeight="1" spans="1:4">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="6" ht="409.5" spans="1:4">
       <c r="D6" s="2" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="7" ht="409.5" customHeight="1" spans="1:4">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="7" ht="409.5" spans="1:4">
       <c r="A7" s="1">
         <v>2</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>71</v>
+        <v>81</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="9" ht="409.5" customHeight="1" spans="1:4">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="9" ht="409.5" spans="1:4">
       <c r="D9" s="2" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="11" ht="409.5" customHeight="1" spans="1:4">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="11" ht="409.5" spans="1:4">
       <c r="D11" s="2" t="s">
-        <v>74</v>
+        <v>84</v>
       </c>
     </row>
   </sheetData>

--- a/AI Audit Log_NguyenVanTuanAnh.xlsx
+++ b/AI Audit Log_NguyenVanTuanAnh.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="7510" firstSheet="2" activeTab="6"/>
+    <workbookView windowWidth="19200" windowHeight="7510" firstSheet="2" activeTab="7"/>
   </bookViews>
   <sheets>
     <sheet name="Week 1" sheetId="1" r:id="rId1"/>
@@ -14,6 +14,7 @@
     <sheet name="Week 5" sheetId="5" r:id="rId5"/>
     <sheet name="Week 6" sheetId="6" r:id="rId6"/>
     <sheet name="Week 7" sheetId="7" r:id="rId7"/>
+    <sheet name="Week 8" sheetId="8" r:id="rId8"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -33,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="95">
   <si>
     <t>STT</t>
   </si>
@@ -334,6 +335,42 @@
   </si>
   <si>
     <t>Quyết định: Chiến lược 2 tầng — (1) token global trong variables.css, (2) override cục bộ có kiểm soát cho status/moderation. Không xóa hết [data-theme="dark"] page-level trong một PR lớn; refactor từng cụm shared (badge, table, card) trước. Mục tiêu: giảm hex trùng, không phá visual đã QA.</t>
+  </si>
+  <si>
+    <t>Shared Staff Sidebar (Giảm trùng lặp)</t>
+  </si>
+  <si>
+    <t>Gộp CSS/drawer sidebar Admin và Moderator đang lặp (overlay, transform, width mobile) vào common/Sidebar/StaffSidebar/staffSidebar.module.css; MainSidebar giữ riêng cho Student shell.</t>
+  </si>
+  <si>
+    <t>Phản hồi: AI phát hiện AdminSidebar và ModeratorSidebar duplicate gần như cùng pattern drawer: overlay, slide-in, width min(...px, ~80vw) dưới breakpoint shell. Đề xuất một staffSidebar.module.css dùng chung; Student MainSidebar/FeedSidebar giữ riêng vì nav khác nghiệp vụ. Shell context (sidebarOpen) + useLockBodyScroll vẫn theo từng layout.</t>
+  </si>
+  <si>
+    <t>Kiểm chứng: DRY đúng chỗ — cùng UX staff drawer không cần 2 bản CSS.
+Tách MainSidebar hợp lý vì Student nav (môn học, cộng đồng) khác Admin/Moderator.
+Cần đảm bảo class name / import sau gộp không gãy build CSS Modules.
+Khi đổi độ rộng drawer mobile chỉ sửa một file → giảm regression lệch giữa 2 role staff.</t>
+  </si>
+  <si>
+    <t>Quyết định: Áp dụng shared StaffSidebar CSS. Không merge luôn MainSidebar vào Staff (khác IA). Chuẩn hóa contract: sidebarOpen từ page/shell context, lock body scroll khi mở. Document trong ARCHITECTURE hoặc comment ngắn: staff drawer = một nguồn CSS.</t>
+  </si>
+  <si>
+    <t>Shared Skeleton + Admin Page Shell</t>
+  </si>
+  <si>
+    <t>Thống nhất skeleton loading Admin/Moderator (StaffSkeleton) và chuẩn hóa AdminPageLayout / breadcrumb / table footer để tránh copy layout và placeholder theo từng trang.</t>
+  </si>
+  <si>
+    <t>Phản hồi: common/Skeleton/StaffSkeleton.jsx + skeletonConstants.js (số hàng chuẩn) là nguồn skeleton bảng/form/queue. features/moderator/components/ModeratorSkeleton chỉ re-export StaffSkeleton — tránh nhân đôi. Admin dùng AdminPageLayout, AdminBreadcrumb, AdminTableFooter, StatusBadge, useAdminPagination trong features/admin/shared/.</t>
+  </si>
+  <si>
+    <t>Kiểm chứng: Re-export ModeratorSkeleton giữ import path cũ → ít breaking change khi refactor.
+Page shell giảm lệch spacing/breadcrumb giữa các màn Admin.
+Skeleton row count chuẩn giúp layout ổn định (ít CLS) hơn spinner đơn.
+Rủi ro: over-abstract layout khiến trang đặc biệt (dashboard chart) bị gò — chỉ áp dụng cho list/form/queue.</t>
+  </si>
+  <si>
+    <t>Quyết định: Giữ StaffSkeleton làm single source; ModeratorSkeleton = thin re-export. Trang Admin list/form mới phải dùng AdminPageLayout + shared footer/pagination. Không ép dashboard chart vào cùng layout cứng — chart giữ ChartResponsiveContainer riêng.</t>
   </si>
 </sst>
 </file>
@@ -992,8 +1029,14 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -1434,7 +1477,7 @@
       <c r="C2" t="s">
         <v>5</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="D2" s="7" t="s">
         <v>6</v>
       </c>
       <c r="H2" t="s">
@@ -1451,7 +1494,7 @@
       <c r="C3" t="s">
         <v>9</v>
       </c>
-      <c r="D3" s="5" t="s">
+      <c r="D3" s="7" t="s">
         <v>10</v>
       </c>
     </row>
@@ -1465,7 +1508,7 @@
       <c r="C4" t="s">
         <v>11</v>
       </c>
-      <c r="D4" s="5" t="s">
+      <c r="D4" s="7" t="s">
         <v>12</v>
       </c>
     </row>
@@ -1479,7 +1522,7 @@
       <c r="C5" t="s">
         <v>13</v>
       </c>
-      <c r="D5" s="5" t="s">
+      <c r="D5" s="7" t="s">
         <v>14</v>
       </c>
     </row>
@@ -1493,21 +1536,21 @@
       <c r="C6" t="s">
         <v>16</v>
       </c>
-      <c r="D6" s="5" t="s">
+      <c r="D6" s="7" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="7" ht="72.5" customHeight="1" spans="1:8">
-      <c r="A7" s="7">
+      <c r="A7" s="9">
         <v>6</v>
       </c>
-      <c r="B7" s="8" t="s">
+      <c r="B7" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="C7" s="8" t="s">
+      <c r="C7" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="D7" s="8" t="s">
+      <c r="D7" s="10" t="s">
         <v>19</v>
       </c>
     </row>
@@ -1538,100 +1581,100 @@
       </c>
     </row>
     <row r="2" ht="409.5" customHeight="1" spans="1:4">
-      <c r="A2" s="7">
+      <c r="A2" s="9">
         <v>1</v>
       </c>
-      <c r="B2" s="8" t="s">
+      <c r="B2" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="8" t="s">
+      <c r="C2" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="D2" s="8" t="s">
+      <c r="D2" s="10" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="3" ht="409.5" customHeight="1" spans="1:4">
-      <c r="A3" s="7">
+      <c r="A3" s="9">
         <v>2</v>
       </c>
-      <c r="B3" s="8" t="s">
+      <c r="B3" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="C3" s="8" t="s">
+      <c r="C3" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="D3" s="8" t="s">
+      <c r="D3" s="10" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="4" ht="409.5" customHeight="1" spans="1:4">
-      <c r="A4" s="7">
+      <c r="A4" s="9">
         <v>3</v>
       </c>
-      <c r="B4" s="8" t="s">
+      <c r="B4" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="C4" s="8" t="s">
+      <c r="C4" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="D4" s="8" t="s">
+      <c r="D4" s="10" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="5" ht="409.5" customHeight="1" spans="1:4">
-      <c r="A5" s="7">
+      <c r="A5" s="9">
         <v>4</v>
       </c>
-      <c r="B5" s="8" t="s">
+      <c r="B5" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="C5" s="8" t="s">
+      <c r="C5" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="D5" s="8" t="s">
+      <c r="D5" s="10" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="6" ht="409.5" customHeight="1" spans="1:4">
-      <c r="A6" s="7">
+      <c r="A6" s="9">
         <v>5</v>
       </c>
-      <c r="B6" s="8" t="s">
+      <c r="B6" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="C6" s="8" t="s">
+      <c r="C6" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="D6" s="8" t="s">
+      <c r="D6" s="10" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="7" ht="409.5" customHeight="1" spans="1:4">
-      <c r="A7" s="7">
+      <c r="A7" s="9">
         <v>6</v>
       </c>
-      <c r="B7" s="8" t="s">
+      <c r="B7" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="C7" s="8" t="s">
+      <c r="C7" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="D7" s="8" t="s">
+      <c r="D7" s="10" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="8" ht="409.5" customHeight="1" spans="1:4">
-      <c r="A8" s="7">
+      <c r="A8" s="9">
         <v>7</v>
       </c>
-      <c r="B8" s="8" t="s">
+      <c r="B8" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="C8" s="8" t="s">
+      <c r="C8" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="D8" s="8" t="s">
+      <c r="D8" s="10" t="s">
         <v>34</v>
       </c>
     </row>
@@ -1667,50 +1710,50 @@
       </c>
     </row>
     <row r="2" ht="232.5" customHeight="1" spans="1:4">
-      <c r="A2" s="5">
+      <c r="A2" s="7">
         <v>1</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="C2" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="D2" s="8" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="4" ht="325.5" customHeight="1" spans="1:4">
-      <c r="D4" s="6" t="s">
+      <c r="D4" s="8" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="6" ht="409.5" customHeight="1" spans="1:4">
-      <c r="D6" s="6" t="s">
+      <c r="D6" s="8" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="7" ht="217" customHeight="1" spans="1:4">
-      <c r="A7" s="5">
+      <c r="A7" s="7">
         <v>2</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B7" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="C7" s="5" t="s">
+      <c r="C7" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="D7" s="6" t="s">
+      <c r="D7" s="8" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="9" ht="409.5" customHeight="1" spans="1:4">
-      <c r="D9" s="6" t="s">
+      <c r="D9" s="8" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="11" ht="409.5" customHeight="1" spans="1:4">
-      <c r="D11" s="6" t="s">
+      <c r="D11" s="8" t="s">
         <v>44</v>
       </c>
     </row>
@@ -1749,50 +1792,50 @@
       </c>
     </row>
     <row r="2" ht="409.5" customHeight="1" spans="1:4">
-      <c r="A2" s="5">
+      <c r="A2" s="7">
         <v>1</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="C2" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="D2" s="8" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="4" ht="409.5" customHeight="1" spans="1:4">
-      <c r="D4" s="6" t="s">
+      <c r="D4" s="8" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="6" ht="409.5" customHeight="1" spans="1:4">
-      <c r="D6" s="6" t="s">
+      <c r="D6" s="8" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="7" ht="409.5" customHeight="1" spans="1:4">
-      <c r="A7" s="5">
+      <c r="A7" s="7">
         <v>2</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B7" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="C7" s="5" t="s">
+      <c r="C7" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="D7" s="6" t="s">
+      <c r="D7" s="8" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="9" ht="409.5" customHeight="1" spans="1:4">
-      <c r="D9" s="6" t="s">
+      <c r="D9" s="8" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="11" ht="409.5" customHeight="1" spans="1:4">
-      <c r="D11" s="6" t="s">
+      <c r="D11" s="8" t="s">
         <v>54</v>
       </c>
     </row>
@@ -1831,50 +1874,50 @@
       </c>
     </row>
     <row r="2" ht="409.5" customHeight="1" spans="1:4">
-      <c r="A2" s="5">
+      <c r="A2" s="7">
         <v>1</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="C2" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="D2" s="8" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="4" ht="409.5" customHeight="1" spans="1:4">
-      <c r="D4" s="6" t="s">
+      <c r="D4" s="8" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="6" ht="409.5" customHeight="1" spans="1:4">
-      <c r="D6" s="6" t="s">
+      <c r="D6" s="8" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="7" ht="409.5" customHeight="1" spans="1:4">
-      <c r="A7" s="5">
+      <c r="A7" s="7">
         <v>2</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B7" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="C7" s="5" t="s">
+      <c r="C7" s="7" t="s">
         <v>61</v>
       </c>
-      <c r="D7" s="6" t="s">
+      <c r="D7" s="8" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="9" ht="409.5" customHeight="1" spans="1:4">
-      <c r="D9" s="6" t="s">
+      <c r="D9" s="8" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="11" ht="409.5" customHeight="1" spans="1:4">
-      <c r="D11" s="6" t="s">
+      <c r="D11" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -1913,50 +1956,50 @@
       </c>
     </row>
     <row r="2" ht="409.5" customHeight="1" spans="1:4">
-      <c r="A2" s="3">
+      <c r="A2" s="5">
         <v>1</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="D2" s="6" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="4" ht="409.5" customHeight="1" spans="1:4">
-      <c r="D4" s="4" t="s">
+      <c r="D4" s="6" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="6" ht="409.5" customHeight="1" spans="1:4">
-      <c r="D6" s="4" t="s">
+      <c r="D6" s="6" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="7" ht="409.5" customHeight="1" spans="1:4">
-      <c r="A7" s="3">
+      <c r="A7" s="5">
         <v>2</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B7" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="C7" s="5" t="s">
         <v>71</v>
       </c>
-      <c r="D7" s="4" t="s">
+      <c r="D7" s="6" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="9" ht="409.5" customHeight="1" spans="1:4">
-      <c r="D9" s="4" t="s">
+      <c r="D9" s="6" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="11" ht="409.5" customHeight="1" spans="1:4">
-      <c r="D11" s="4" t="s">
+      <c r="D11" s="6" t="s">
         <v>74</v>
       </c>
     </row>
@@ -1995,27 +2038,109 @@
       </c>
     </row>
     <row r="2" ht="409.5" spans="1:4">
+      <c r="A2" s="3">
+        <v>1</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="4" ht="409.5" spans="1:4">
+      <c r="D4" s="4" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="6" ht="409.5" spans="1:4">
+      <c r="D6" s="4" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="7" ht="409.5" spans="1:4">
+      <c r="A7" s="3">
+        <v>2</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="9" ht="409.5" spans="1:4">
+      <c r="D9" s="4" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="11" ht="409.5" spans="1:4">
+      <c r="D11" s="4" t="s">
+        <v>84</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A2:A6"/>
+    <mergeCell ref="A7:A11"/>
+    <mergeCell ref="B2:B6"/>
+    <mergeCell ref="B7:B11"/>
+    <mergeCell ref="C2:C6"/>
+    <mergeCell ref="C7:C11"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:D11"/>
+  <sheetFormatPr defaultColWidth="8.66666666666667" defaultRowHeight="15.5" outlineLevelCol="3"/>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" ht="409.5" spans="1:4">
       <c r="A2" s="1">
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>77</v>
+        <v>87</v>
       </c>
     </row>
     <row r="4" ht="409.5" spans="1:4">
       <c r="D4" s="2" t="s">
-        <v>78</v>
+        <v>88</v>
       </c>
     </row>
     <row r="6" ht="409.5" spans="1:4">
       <c r="D6" s="2" t="s">
-        <v>79</v>
+        <v>89</v>
       </c>
     </row>
     <row r="7" ht="409.5" spans="1:4">
@@ -2023,23 +2148,23 @@
         <v>2</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>82</v>
+        <v>92</v>
       </c>
     </row>
     <row r="9" ht="409.5" spans="1:4">
       <c r="D9" s="2" t="s">
-        <v>83</v>
+        <v>93</v>
       </c>
     </row>
     <row r="11" ht="409.5" spans="1:4">
       <c r="D11" s="2" t="s">
-        <v>84</v>
+        <v>94</v>
       </c>
     </row>
   </sheetData>

--- a/AI Audit Log_NguyenVanTuanAnh.xlsx
+++ b/AI Audit Log_NguyenVanTuanAnh.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="7510" firstSheet="2" activeTab="7"/>
+    <workbookView windowWidth="19200" windowHeight="7510" firstSheet="2" activeTab="8"/>
   </bookViews>
   <sheets>
     <sheet name="Week 1" sheetId="1" r:id="rId1"/>
@@ -15,6 +15,7 @@
     <sheet name="Week 6" sheetId="6" r:id="rId6"/>
     <sheet name="Week 7" sheetId="7" r:id="rId7"/>
     <sheet name="Week 8" sheetId="8" r:id="rId8"/>
+    <sheet name="Week 9" sheetId="9" r:id="rId9"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -34,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="105">
   <si>
     <t>STT</t>
   </si>
@@ -371,6 +372,42 @@
   </si>
   <si>
     <t>Quyết định: Giữ StaffSkeleton làm single source; ModeratorSkeleton = thin re-export. Trang Admin list/form mới phải dùng AdminPageLayout + shared footer/pagination. Không ép dashboard chart vào cùng layout cứng — chart giữ ChartResponsiveContainer riêng.</t>
+  </si>
+  <si>
+    <t>Route Lazy Loading + Vite manualChunks</t>
+  </si>
+  <si>
+    <t>Kiểm tra và tối ưu bundle Front-end SEHUB: lazy() + Suspense cho route Admin/Moderator/Documents trong App.jsx; cấu hình manualChunks (react, recharts, signalr) trong vite.config.js.</t>
+  </si>
+  <si>
+    <t>Phản hồi: App.jsx dùng React.lazy cho nhiều page nặng (admin, moderator, documents…), bọc Suspense với fallback hợp lý. vite.config.js tách vendor: react, recharts, signalr thành chunk riêng — giảm parse cost trang Student không mở dashboard/chat realtime. Alias @ → src giữ nguyên.</t>
+  </si>
+  <si>
+    <t>Kiểm chứng: Code-split theo route phù hợp SPA nhiều role — Guest/Student không tải sẵn toàn bộ Admin.
+manualChunks vendor ổn định cache giữa lần deploy nếu app code đổi.
+Không nên split quá mảnh từng component nhỏ (waterfall request).
+Cần fallback Suspense không trống (AuthBootstrapFallback / skeleton) để UX mượt.</t>
+  </si>
+  <si>
+    <t>Quyết định: Giữ lazy theo nhóm route + 3 manualChunks hiện tại. Không thêm memo/useMemo hàng loạt như "tối ưu" — ưu tiên split bundle và loading UX trước. Đo lại bằng build analyzer nếu bundle recharts vẫn lớn trên trang có chart.</t>
+  </si>
+  <si>
+    <t>Skeleton UX + Debounced Search</t>
+  </si>
+  <si>
+    <t>Tối ưu cảm nhận tải và giảm spam API: dùng Skeleton/Shimmer cho list/table; áp dụng useDebouncedValue cho ô tìm kiếm (Search, ViolatingAccounts…).</t>
+  </si>
+  <si>
+    <t>Phản hồi: common/Skeleton (Shimmer, SkeletonList, StaffSkeleton) thay spinner trần trên nhiều màn. useDebouncedValue.js trì hoãn giá trị search trước khi gọi API. ConversationChat dùng @tanstack/react-virtual cho list tin dài — tối ưu render, không chỉ network.</t>
+  </si>
+  <si>
+    <t>Kiểm chứng: Skeleton giảm cảm giác chờ và giữ layout (ít nhảy UI) — phù hợp audit "tối ưu FE" hơn premature memo.
+Debounce search cắt request khi gõ nhanh — quan trọng với moderator/admin filter.
+Virtual list chỉ cần nơi list rất dài (chat); không áp dụng đại trà.
+Cân nhắc delay debounce ~300ms: quá thấp vẫn spam, quá cao cảm giác đơ.</t>
+  </si>
+  <si>
+    <t>Quyết định: Ưu tiên skeleton + debounce + virtual hóa điểm nóng. Chuẩn hóa import skeleton từ common/; trang mới không tự invent spinner khác. Debounce mặc định thống nhất qua hook (tránh setTimeout copy-paste). Virtualization giữ phạm vi chat trừ khi list khác vượt ngưỡng performance.</t>
   </si>
 </sst>
 </file>
@@ -2120,27 +2157,109 @@
       </c>
     </row>
     <row r="2" ht="409.5" spans="1:4">
+      <c r="A2" s="3">
+        <v>1</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="4" ht="409.5" spans="1:4">
+      <c r="D4" s="4" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="6" ht="409.5" spans="1:4">
+      <c r="D6" s="4" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="7" ht="409.5" spans="1:4">
+      <c r="A7" s="3">
+        <v>2</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="9" ht="409.5" spans="1:4">
+      <c r="D9" s="4" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="11" ht="409.5" spans="1:4">
+      <c r="D11" s="4" t="s">
+        <v>94</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A2:A6"/>
+    <mergeCell ref="A7:A11"/>
+    <mergeCell ref="B2:B6"/>
+    <mergeCell ref="B7:B11"/>
+    <mergeCell ref="C2:C6"/>
+    <mergeCell ref="C7:C11"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:D11"/>
+  <sheetFormatPr defaultColWidth="8.66666666666667" defaultRowHeight="15.5" outlineLevelCol="3"/>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" ht="409.5" spans="1:4">
       <c r="A2" s="1">
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>86</v>
+        <v>96</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>87</v>
+        <v>97</v>
       </c>
     </row>
     <row r="4" ht="409.5" spans="1:4">
       <c r="D4" s="2" t="s">
-        <v>88</v>
+        <v>98</v>
       </c>
     </row>
     <row r="6" ht="409.5" spans="1:4">
       <c r="D6" s="2" t="s">
-        <v>89</v>
+        <v>99</v>
       </c>
     </row>
     <row r="7" ht="409.5" spans="1:4">
@@ -2148,23 +2267,23 @@
         <v>2</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>91</v>
+        <v>101</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
     </row>
     <row r="9" ht="409.5" spans="1:4">
       <c r="D9" s="2" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
     </row>
     <row r="11" ht="409.5" spans="1:4">
       <c r="D11" s="2" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
     </row>
   </sheetData>

--- a/AI Audit Log_NguyenVanTuanAnh.xlsx
+++ b/AI Audit Log_NguyenVanTuanAnh.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="7510" firstSheet="2" activeTab="8"/>
+    <workbookView windowWidth="19200" windowHeight="7510" firstSheet="2" activeTab="9"/>
   </bookViews>
   <sheets>
     <sheet name="Week 1" sheetId="1" r:id="rId1"/>
@@ -16,6 +16,7 @@
     <sheet name="Week 7" sheetId="7" r:id="rId7"/>
     <sheet name="Week 8" sheetId="8" r:id="rId8"/>
     <sheet name="Week 9" sheetId="9" r:id="rId9"/>
+    <sheet name="Week 10" sheetId="10" r:id="rId10"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -35,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="115">
   <si>
     <t>STT</t>
   </si>
@@ -408,6 +409,43 @@
   </si>
   <si>
     <t>Quyết định: Ưu tiên skeleton + debounce + virtual hóa điểm nóng. Chuẩn hóa import skeleton từ common/; trang mới không tự invent spinner khác. Debounce mặc định thống nhất qua hook (tránh setTimeout copy-paste). Virtualization giữ phạm vi chat trừ khi list khác vượt ngưỡng performance.</t>
+  </si>
+  <si>
+    <t>Breakpoint Tokens + Mobile Drawer Shell</t>
+  </si>
+  <si>
+    <t>Chuẩn hóa breakpoint CSS (--bp-shell 1024, --bp-nav 900, --bp-tablet 768, --bp-phone 640, --bp-phone-sm 480) và kiểm tra drawer sidebar Student/Staff/Feed dưới max-width 1024px kèm lock body scroll.</t>
+  </si>
+  <si>
+    <t>Phản hồi: breakpoints.css + variables.css document token --bp-*. Utility .tableWrap, .stackOnPhone, .hideOnPhone, .showOnPhone. Dưới --bp-shell (1024): MainSidebar, StaffSidebar, FeedSidebar chuyển drawer (overlay + transform). MainShellContext / staff page context giữ sidebarOpen; useLockBodyScroll khóa scroll nền khi drawer mở.</t>
+  </si>
+  <si>
+    <t>Kiểm chứng: Một thang breakpoint tránh magic number lệch giữa file CSS Modules.
+1024 làm mốc shell hợp lý (tablet ngang vẫn dùng drawer).
+Drawer width min(fixed, ~80vw) tránh tràn phone nhỏ.
+ContentModerationPage dùng matchMedia(~1023px) cho split list/detail — cần khớp token shell để không lệch UX.
+Lock body scroll bắt buộc, không thì scroll "lọt" xuống nội dung dưới overlay.</t>
+  </si>
+  <si>
+    <t>Quyết định: Mọi media query shell/sidebar mới phải dùng token --bp-* (hoặc cùng giá trị đã document). Không invent breakpoint lẻ (ví dụ 999px). Drawer pattern thống nhất qua StaffSidebar CSS + MainSidebar. Bổ sung checklist QA: mở/đóng drawer, overlay click, scroll lock trên phone thật hoặc DevTools.</t>
+  </si>
+  <si>
+    <t>GuestHeader Mobile + Responsive Preview QA</t>
+  </si>
+  <si>
+    <t>Hoàn thiện GuestHeader mobile (hamburger, ThemeSwitcher compact) và dùng responsive-preview.html / responsive-preview-single.html / responsive-preview-regression.html để QA multi-viewport trước khi merge fix responsive.</t>
+  </si>
+  <si>
+    <t>Phản hồi: GuestHeader cần nav rút gọn + hamburger ở viewport hẹp; ThemeSwitcher bản compact để không đẩy CTA Đăng nhập. Bộ file fe/public/responsive-preview*.html cho phép soi nhiều route/viewport (shell, regression) không cần deploy. Các PR responsive (drawer hẹp, plan S1–S4 Guest) dựa trên checklist này.</t>
+  </si>
+  <si>
+    <t>Kiểm chứng: Guest là mặt tiền marketing/community — mobile-first quan trọng không kém Student shell.
+Preview HTML tĩnh không thay E2E nhưng đủ bắt lỗi layout nhanh (sidebar đè, header vỡ).
+Compact theme switcher phải đồng bộ preference với bản menu desktop.
+Regression preview giúp so sánh trước/sau khi đụng breakpoints.css toàn cục.</t>
+  </si>
+  <si>
+    <t>Quyết định: Coi responsive-preview*.html là bước QA thủ công bắt buộc với thay đổi shell/header/sidebar. GuestHeader mobile + drawer staff/student là xong phase responsive cốt lõi. Tiếp theo chỉ fix page-level (bảng admin wrap, stack form) theo utility breakpoints, không đổi lại mốc --bp-shell trừ khi có lý do đo đạc rõ.</t>
   </si>
 </sst>
 </file>
@@ -1597,6 +1635,88 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:D11"/>
+  <sheetFormatPr defaultColWidth="8.66666666666667" defaultRowHeight="15.5" outlineLevelCol="3"/>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" ht="409.5" spans="1:4">
+      <c r="A2" s="1">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="4" ht="409.5" spans="1:4">
+      <c r="D4" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="6" ht="409.5" spans="1:4">
+      <c r="D6" s="2" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="7" ht="409.5" spans="1:4">
+      <c r="A7" s="1">
+        <v>2</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="9" ht="409.5" spans="1:4">
+      <c r="D9" s="2" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="11" ht="409.5" spans="1:4">
+      <c r="D11" s="2" t="s">
+        <v>114</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A2:A6"/>
+    <mergeCell ref="A7:A11"/>
+    <mergeCell ref="B2:B6"/>
+    <mergeCell ref="B7:B11"/>
+    <mergeCell ref="C2:C6"/>
+    <mergeCell ref="C7:C11"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
@@ -2239,50 +2359,50 @@
       </c>
     </row>
     <row r="2" ht="409.5" spans="1:4">
-      <c r="A2" s="1">
+      <c r="A2" s="3">
         <v>1</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="4" t="s">
         <v>97</v>
       </c>
     </row>
     <row r="4" ht="409.5" spans="1:4">
-      <c r="D4" s="2" t="s">
+      <c r="D4" s="4" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="6" ht="409.5" spans="1:4">
-      <c r="D6" s="2" t="s">
+      <c r="D6" s="4" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="7" ht="409.5" spans="1:4">
-      <c r="A7" s="1">
+      <c r="A7" s="3">
         <v>2</v>
       </c>
-      <c r="B7" s="1" t="s">
+      <c r="B7" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="C7" s="1" t="s">
+      <c r="C7" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="D7" s="4" t="s">
         <v>102</v>
       </c>
     </row>
     <row r="9" ht="409.5" spans="1:4">
-      <c r="D9" s="2" t="s">
+      <c r="D9" s="4" t="s">
         <v>103</v>
       </c>
     </row>
     <row r="11" ht="409.5" spans="1:4">
-      <c r="D11" s="2" t="s">
+      <c r="D11" s="4" t="s">
         <v>104</v>
       </c>
     </row>
